--- a/AZ WEIGHT MASTER.xlsx
+++ b/AZ WEIGHT MASTER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JK FENNER\p\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528412EF-B0BB-4441-941D-45C4547FFEC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322F5259-4782-4FED-9111-F54CEA2D9251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5671,18 +5671,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -8941,7 +8930,7 @@
         <v>1.24</v>
       </c>
       <c r="D141" s="2">
-        <v>0.1</v>
+        <v>-0.10000000000000003</v>
       </c>
       <c r="E141" s="2">
         <v>2</v>
@@ -9382,7 +9371,7 @@
         <v>1.27</v>
       </c>
       <c r="D162" s="2">
-        <v>0.17</v>
+        <v>-0.16999999999999998</v>
       </c>
       <c r="E162" s="2">
         <v>7</v>
@@ -10159,7 +10148,7 @@
         <v>1.5899999999999999</v>
       </c>
       <c r="D199" s="2">
-        <v>9.0000000000000094E-2</v>
+        <v>-9.000000000000008E-2</v>
       </c>
       <c r="E199" s="2">
         <v>10</v>
@@ -10201,7 +10190,7 @@
         <v>1.5899999999999999</v>
       </c>
       <c r="D201" s="2">
-        <v>9.0000000000000094E-2</v>
+        <v>-9.000000000000008E-2</v>
       </c>
       <c r="E201" s="2">
         <v>10</v>
@@ -10327,7 +10316,7 @@
         <v>1.5899999999999999</v>
       </c>
       <c r="D207" s="2">
-        <v>9.0000000000000094E-2</v>
+        <v>-9.000000000000008E-2</v>
       </c>
       <c r="E207" s="2">
         <v>10</v>
@@ -11545,7 +11534,7 @@
         <v>1.34</v>
       </c>
       <c r="D265" s="2">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E265" s="2">
         <v>5</v>
@@ -11902,7 +11891,7 @@
         <v>1.34</v>
       </c>
       <c r="D282" s="2">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E282" s="2">
         <v>5</v>
@@ -12091,7 +12080,7 @@
         <v>1.49</v>
       </c>
       <c r="D291" s="2">
-        <v>0.08</v>
+        <v>-7.999999999999996E-2</v>
       </c>
       <c r="E291" s="2">
         <v>11</v>
@@ -12133,7 +12122,7 @@
         <v>1.34</v>
       </c>
       <c r="D293" s="2">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E293" s="2">
         <v>5</v>
@@ -12322,7 +12311,7 @@
         <v>1.27</v>
       </c>
       <c r="D302" s="2">
-        <v>0.17</v>
+        <v>-0.16999999999999998</v>
       </c>
       <c r="E302" s="2">
         <v>7</v>
@@ -12805,7 +12794,7 @@
         <v>1.34</v>
       </c>
       <c r="D325" s="2">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E325" s="2">
         <v>5</v>
@@ -12826,7 +12815,7 @@
         <v>1.34</v>
       </c>
       <c r="D326" s="2">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E326" s="2">
         <v>5</v>
@@ -13624,7 +13613,7 @@
         <v>1.6099999999999999</v>
       </c>
       <c r="D364" s="2">
-        <v>0.39</v>
+        <v>-0.39</v>
       </c>
       <c r="E364" s="2">
         <v>6</v>
@@ -13708,7 +13697,7 @@
         <v>1.34</v>
       </c>
       <c r="D368" s="2">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E368" s="2">
         <v>5</v>
@@ -13855,7 +13844,7 @@
         <v>1.5899999999999999</v>
       </c>
       <c r="D375" s="2">
-        <v>9.0000000000000094E-2</v>
+        <v>-9.000000000000008E-2</v>
       </c>
       <c r="E375" s="2">
         <v>10</v>
@@ -14086,7 +14075,7 @@
         <v>1.5899999999999999</v>
       </c>
       <c r="D386" s="2">
-        <v>9.0000000000000094E-2</v>
+        <v>-9.000000000000008E-2</v>
       </c>
       <c r="E386" s="2">
         <v>10</v>
@@ -14695,7 +14684,7 @@
         <v>1.6099999999999999</v>
       </c>
       <c r="D415" s="2">
-        <v>0.39</v>
+        <v>-0.39</v>
       </c>
       <c r="E415" s="2">
         <v>6</v>
@@ -14758,7 +14747,7 @@
         <v>1.6099999999999999</v>
       </c>
       <c r="D418" s="2">
-        <v>0.35</v>
+        <v>-0.35</v>
       </c>
       <c r="E418" s="2">
         <v>14</v>
@@ -14779,7 +14768,7 @@
         <v>1.6099999999999999</v>
       </c>
       <c r="D419" s="2">
-        <v>0.35</v>
+        <v>-0.35</v>
       </c>
       <c r="E419" s="2">
         <v>14</v>
@@ -14884,7 +14873,7 @@
         <v>1.5899999999999999</v>
       </c>
       <c r="D424" s="2">
-        <v>9.0000000000000094E-2</v>
+        <v>-9.000000000000008E-2</v>
       </c>
       <c r="E424" s="2">
         <v>10</v>
@@ -15682,7 +15671,7 @@
         <v>1.34</v>
       </c>
       <c r="D462" s="2">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E462" s="2">
         <v>5</v>
@@ -15787,7 +15776,7 @@
         <v>1.34</v>
       </c>
       <c r="D467" s="2">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E467" s="2">
         <v>5</v>
@@ -16060,7 +16049,7 @@
         <v>1.34</v>
       </c>
       <c r="D480" s="2">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E480" s="2">
         <v>5</v>
@@ -16081,7 +16070,7 @@
         <v>1.34</v>
       </c>
       <c r="D481" s="2">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E481" s="2">
         <v>5</v>
@@ -16228,7 +16217,7 @@
         <v>1.58</v>
       </c>
       <c r="D488" s="2">
-        <v>0.22</v>
+        <v>-0.22000000000000008</v>
       </c>
       <c r="E488" s="2">
         <v>12</v>
@@ -17026,7 +17015,7 @@
         <v>1.6099999999999999</v>
       </c>
       <c r="D526" s="2">
-        <v>0.35</v>
+        <v>-0.35</v>
       </c>
       <c r="E526" s="2">
         <v>14</v>
@@ -17698,7 +17687,7 @@
         <v>1.49</v>
       </c>
       <c r="D558" s="2">
-        <v>0.08</v>
+        <v>-7.999999999999996E-2</v>
       </c>
       <c r="E558" s="2">
         <v>11</v>
@@ -17740,7 +17729,7 @@
         <v>1.6099999999999999</v>
       </c>
       <c r="D560" s="2">
-        <v>0.39</v>
+        <v>-0.39</v>
       </c>
       <c r="E560" s="2">
         <v>6</v>
@@ -18097,7 +18086,7 @@
         <v>1.6099999999999999</v>
       </c>
       <c r="D577" s="2">
-        <v>0.39</v>
+        <v>-0.39</v>
       </c>
       <c r="E577" s="2">
         <v>6</v>
@@ -18286,7 +18275,7 @@
         <v>1.5899999999999999</v>
       </c>
       <c r="D586" s="2">
-        <v>9.0000000000000094E-2</v>
+        <v>-9.000000000000008E-2</v>
       </c>
       <c r="E586" s="2">
         <v>10</v>
@@ -18727,7 +18716,7 @@
         <v>1.41</v>
       </c>
       <c r="D607" s="2">
-        <v>0.21</v>
+        <v>-0.21000000000000002</v>
       </c>
       <c r="E607" s="2">
         <v>4</v>
@@ -18895,7 +18884,7 @@
         <v>1.6099999999999999</v>
       </c>
       <c r="D615" s="2">
-        <v>0.39</v>
+        <v>-0.39</v>
       </c>
       <c r="E615" s="2">
         <v>6</v>
@@ -18937,7 +18926,7 @@
         <v>1.76</v>
       </c>
       <c r="D617" s="2">
-        <v>0.52</v>
+        <v>-0.52</v>
       </c>
       <c r="E617" s="2">
         <v>13</v>
@@ -19105,7 +19094,7 @@
         <v>1.6099999999999999</v>
       </c>
       <c r="D625" s="2">
-        <v>0.39</v>
+        <v>-0.39</v>
       </c>
       <c r="E625" s="2">
         <v>6</v>
@@ -19126,7 +19115,7 @@
         <v>1.76</v>
       </c>
       <c r="D626" s="2">
-        <v>0.52</v>
+        <v>-0.52</v>
       </c>
       <c r="E626" s="2">
         <v>13</v>
@@ -19378,7 +19367,7 @@
         <v>1.6099999999999999</v>
       </c>
       <c r="D638" s="2">
-        <v>0.39</v>
+        <v>-0.39</v>
       </c>
       <c r="E638" s="2">
         <v>6</v>
@@ -19441,7 +19430,7 @@
         <v>1.17</v>
       </c>
       <c r="D641" s="2">
-        <v>0.59</v>
+        <v>-0.59000000000000008</v>
       </c>
       <c r="E641" s="2">
         <v>17</v>
@@ -19504,7 +19493,7 @@
         <v>1.17</v>
       </c>
       <c r="D644" s="2">
-        <v>0.59</v>
+        <v>-0.59000000000000008</v>
       </c>
       <c r="E644" s="2">
         <v>17</v>
@@ -19672,7 +19661,7 @@
         <v>1.17</v>
       </c>
       <c r="D652" s="2">
-        <v>0.59</v>
+        <v>-0.59000000000000008</v>
       </c>
       <c r="E652" s="2">
         <v>17</v>
@@ -19777,7 +19766,7 @@
         <v>1.58</v>
       </c>
       <c r="D657" s="2">
-        <v>0.22</v>
+        <v>-0.22000000000000008</v>
       </c>
       <c r="E657" s="2">
         <v>12</v>
@@ -19840,7 +19829,7 @@
         <v>1.34</v>
       </c>
       <c r="D660" s="2">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E660" s="2">
         <v>5</v>
@@ -19861,7 +19850,7 @@
         <v>1.41</v>
       </c>
       <c r="D661" s="2">
-        <v>0.21</v>
+        <v>-0.21000000000000002</v>
       </c>
       <c r="E661" s="2">
         <v>4</v>
@@ -20428,7 +20417,7 @@
         <v>1.76</v>
       </c>
       <c r="D688" s="2">
-        <v>0.52</v>
+        <v>-0.52</v>
       </c>
       <c r="E688" s="2">
         <v>13</v>
@@ -20701,7 +20690,7 @@
         <v>1.41</v>
       </c>
       <c r="D701" s="2">
-        <v>0.21</v>
+        <v>-0.21000000000000002</v>
       </c>
       <c r="E701" s="2">
         <v>4</v>
@@ -20995,7 +20984,7 @@
         <v>1.6099999999999999</v>
       </c>
       <c r="D715" s="2">
-        <v>0.39</v>
+        <v>-0.39</v>
       </c>
       <c r="E715" s="2">
         <v>6</v>
@@ -21289,7 +21278,7 @@
         <v>1.5899999999999999</v>
       </c>
       <c r="D729" s="2">
-        <v>9.0000000000000094E-2</v>
+        <v>-9.000000000000008E-2</v>
       </c>
       <c r="E729" s="2">
         <v>10</v>
@@ -21436,7 +21425,7 @@
         <v>1.41</v>
       </c>
       <c r="D736" s="2">
-        <v>0.21</v>
+        <v>-0.21000000000000002</v>
       </c>
       <c r="E736" s="2">
         <v>4</v>
@@ -21793,7 +21782,7 @@
         <v>1.17</v>
       </c>
       <c r="D753" s="2">
-        <v>0.59</v>
+        <v>-0.59000000000000008</v>
       </c>
       <c r="E753" s="2">
         <v>17</v>
@@ -21961,7 +21950,7 @@
         <v>1.17</v>
       </c>
       <c r="D761" s="2">
-        <v>0.59</v>
+        <v>-0.59000000000000008</v>
       </c>
       <c r="E761" s="2">
         <v>17</v>
@@ -22003,7 +21992,7 @@
         <v>1.5899999999999999</v>
       </c>
       <c r="D763" s="2">
-        <v>9.0000000000000094E-2</v>
+        <v>-9.000000000000008E-2</v>
       </c>
       <c r="E763" s="2">
         <v>10</v>
@@ -22024,7 +22013,7 @@
         <v>1.76</v>
       </c>
       <c r="D764" s="2">
-        <v>0.52</v>
+        <v>-0.52</v>
       </c>
       <c r="E764" s="2">
         <v>13</v>
@@ -22045,7 +22034,7 @@
         <v>1.76</v>
       </c>
       <c r="D765" s="2">
-        <v>0.52</v>
+        <v>-0.52</v>
       </c>
       <c r="E765" s="2">
         <v>13</v>
@@ -22276,7 +22265,7 @@
         <v>1.76</v>
       </c>
       <c r="D776" s="2">
-        <v>0.52</v>
+        <v>-0.52</v>
       </c>
       <c r="E776" s="2">
         <v>13</v>
@@ -22780,7 +22769,7 @@
         <v>1.76</v>
       </c>
       <c r="D800" s="2">
-        <v>0.52</v>
+        <v>-0.52</v>
       </c>
       <c r="E800" s="2">
         <v>13</v>
@@ -22801,7 +22790,7 @@
         <v>1.41</v>
       </c>
       <c r="D801" s="2">
-        <v>0.21</v>
+        <v>-0.21000000000000002</v>
       </c>
       <c r="E801" s="2">
         <v>4</v>
@@ -23473,7 +23462,7 @@
         <v>1.69</v>
       </c>
       <c r="D833" s="2">
-        <v>0.43</v>
+        <v>-0.43000000000000016</v>
       </c>
       <c r="E833" s="2">
         <v>16</v>
@@ -23599,7 +23588,7 @@
         <v>1.76</v>
       </c>
       <c r="D839" s="2">
-        <v>0.52</v>
+        <v>-0.52</v>
       </c>
       <c r="E839" s="2">
         <v>13</v>
@@ -23998,7 +23987,7 @@
         <v>1.17</v>
       </c>
       <c r="D858" s="2">
-        <v>0.59</v>
+        <v>-0.59000000000000008</v>
       </c>
       <c r="E858" s="2">
         <v>17</v>
@@ -24019,7 +24008,7 @@
         <v>1.6099999999999999</v>
       </c>
       <c r="D859" s="2">
-        <v>0.35</v>
+        <v>-0.35</v>
       </c>
       <c r="E859" s="2">
         <v>14</v>
@@ -24166,7 +24155,7 @@
         <v>1.6099999999999999</v>
       </c>
       <c r="D866" s="2">
-        <v>0.35</v>
+        <v>-0.35</v>
       </c>
       <c r="E866" s="2">
         <v>14</v>
@@ -24292,7 +24281,7 @@
         <v>1.5899999999999999</v>
       </c>
       <c r="D872" s="2">
-        <v>9.0000000000000094E-2</v>
+        <v>-9.000000000000008E-2</v>
       </c>
       <c r="E872" s="2">
         <v>10</v>
@@ -24481,7 +24470,7 @@
         <v>1.6099999999999999</v>
       </c>
       <c r="D881" s="2">
-        <v>0.39</v>
+        <v>-0.39</v>
       </c>
       <c r="E881" s="2">
         <v>6</v>
@@ -25006,7 +24995,7 @@
         <v>1.69</v>
       </c>
       <c r="D906" s="2">
-        <v>0.43</v>
+        <v>-0.43000000000000016</v>
       </c>
       <c r="E906" s="2">
         <v>16</v>
@@ -25111,7 +25100,7 @@
         <v>1.34</v>
       </c>
       <c r="D911" s="2">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E911" s="2">
         <v>5</v>
@@ -25216,7 +25205,7 @@
         <v>1.69</v>
       </c>
       <c r="D916" s="2">
-        <v>0.43</v>
+        <v>-0.43000000000000016</v>
       </c>
       <c r="E916" s="2">
         <v>16</v>
@@ -25458,11 +25447,6 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>